--- a/app/IVR_Sheet.xlsx
+++ b/app/IVR_Sheet.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FJ201"/>
+  <dimension ref="A1:FL201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1288,6 +1288,16 @@
           <t>Battery Owned</t>
         </is>
       </c>
+      <c r="FK2" t="inlineStr">
+        <is>
+          <t>Seats</t>
+        </is>
+      </c>
+      <c r="FL2" t="inlineStr">
+        <is>
+          <t>Luxury</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="C3" t="inlineStr">
@@ -1358,6 +1368,16 @@
       <c r="P3" t="inlineStr">
         <is>
           <t>e.g. B2</t>
+        </is>
+      </c>
+      <c r="FK3" t="inlineStr">
+        <is>
+          <t>numeric seat count, e.g. 5</t>
+        </is>
+      </c>
+      <c r="FL3" t="inlineStr">
+        <is>
+          <t>YES if luxury, else NO</t>
         </is>
       </c>
     </row>
@@ -1425,6 +1445,14 @@
           <t>S</t>
         </is>
       </c>
+      <c r="FK4" t="n">
+        <v>5</v>
+      </c>
+      <c r="FL4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="B5" t="n">
@@ -1492,6 +1520,14 @@
           <t>S</t>
         </is>
       </c>
+      <c r="FK5" t="n">
+        <v>5</v>
+      </c>
+      <c r="FL5" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="B6" t="n">
@@ -1557,6 +1593,14 @@
           <t>S</t>
         </is>
       </c>
+      <c r="FK6" t="n">
+        <v>5</v>
+      </c>
+      <c r="FL6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="B7" t="n">
@@ -1627,6 +1671,14 @@
           <t>S</t>
         </is>
       </c>
+      <c r="FK7" t="n">
+        <v>5</v>
+      </c>
+      <c r="FL7" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="B8" t="n">
@@ -1692,6 +1744,14 @@
           <t>S</t>
         </is>
       </c>
+      <c r="FK8" t="n">
+        <v>5</v>
+      </c>
+      <c r="FL8" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="B9" t="n">
@@ -1759,6 +1819,14 @@
           <t>S</t>
         </is>
       </c>
+      <c r="FK9" t="n">
+        <v>5</v>
+      </c>
+      <c r="FL9" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="B10" t="n">
@@ -1824,6 +1892,11 @@
           <t>S</t>
         </is>
       </c>
+      <c r="FL10" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="B11" t="n">
@@ -1894,6 +1967,11 @@
           <t>S</t>
         </is>
       </c>
+      <c r="FL11" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="B12" t="n">
@@ -1957,6 +2035,11 @@
       <c r="R12" t="n">
         <v>2027</v>
       </c>
+      <c r="FL12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="B13" t="n">
@@ -2025,6 +2108,11 @@
           <t>S</t>
         </is>
       </c>
+      <c r="FL13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="B14" t="n">
@@ -2090,6 +2178,11 @@
           <t>S</t>
         </is>
       </c>
+      <c r="FL14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="B15" t="n">
@@ -2153,6 +2246,14 @@
       <c r="R15" t="n">
         <v>2029</v>
       </c>
+      <c r="FK15" t="n">
+        <v>5</v>
+      </c>
+      <c r="FL15" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="B16" t="n">
@@ -2213,6 +2314,14 @@
       <c r="R16" t="n">
         <v>2032</v>
       </c>
+      <c r="FK16" t="n">
+        <v>5</v>
+      </c>
+      <c r="FL16" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="B17" t="n">
@@ -2276,6 +2385,14 @@
       <c r="R17" t="n">
         <v>2033</v>
       </c>
+      <c r="FK17" t="n">
+        <v>5</v>
+      </c>
+      <c r="FL17" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="B18" t="n">
@@ -2341,6 +2458,14 @@
           <t>S</t>
         </is>
       </c>
+      <c r="FK18" t="n">
+        <v>5</v>
+      </c>
+      <c r="FL18" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="B19" t="n">
@@ -2406,6 +2531,14 @@
           <t>.</t>
         </is>
       </c>
+      <c r="FK19" t="n">
+        <v>5</v>
+      </c>
+      <c r="FL19" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="B20" t="n">
@@ -2469,6 +2602,14 @@
       <c r="R20" t="n">
         <v>2029</v>
       </c>
+      <c r="FK20" t="n">
+        <v>7</v>
+      </c>
+      <c r="FL20" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="B21" t="n">
@@ -2529,6 +2670,14 @@
       <c r="R21" t="n">
         <v>2027</v>
       </c>
+      <c r="FK21" t="n">
+        <v>5</v>
+      </c>
+      <c r="FL21" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="B22" t="n">
@@ -2589,6 +2738,14 @@
       <c r="R22" t="n">
         <v>2028</v>
       </c>
+      <c r="FK22" t="n">
+        <v>5</v>
+      </c>
+      <c r="FL22" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="B23" t="n">
@@ -2649,6 +2806,14 @@
       <c r="R23" t="n">
         <v>2033</v>
       </c>
+      <c r="FK23" t="n">
+        <v>7</v>
+      </c>
+      <c r="FL23" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="B24" t="n">
@@ -2714,6 +2879,14 @@
           <t>.</t>
         </is>
       </c>
+      <c r="FK24" t="n">
+        <v>7</v>
+      </c>
+      <c r="FL24" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="B25" t="n">
@@ -2779,6 +2952,14 @@
           <t>S</t>
         </is>
       </c>
+      <c r="FK25" t="n">
+        <v>5</v>
+      </c>
+      <c r="FL25" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="B26" t="n">
@@ -2836,6 +3017,14 @@
       <c r="R26" t="n">
         <v>2031</v>
       </c>
+      <c r="FK26" t="n">
+        <v>5</v>
+      </c>
+      <c r="FL26" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="B27" t="n">
@@ -2896,6 +3085,14 @@
       <c r="R27" t="n">
         <v>2031</v>
       </c>
+      <c r="FK27" t="n">
+        <v>5</v>
+      </c>
+      <c r="FL27" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="B28" t="n">
@@ -2956,6 +3153,14 @@
       <c r="R28" t="n">
         <v>2032</v>
       </c>
+      <c r="FK28" t="n">
+        <v>5</v>
+      </c>
+      <c r="FL28" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="B29" t="n">
@@ -3016,6 +3221,11 @@
       <c r="R29" t="n">
         <v>2029</v>
       </c>
+      <c r="FL29" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="B30" t="n">
@@ -3076,6 +3286,11 @@
       <c r="R30" t="n">
         <v>2029</v>
       </c>
+      <c r="FL30" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="B31" t="n">
@@ -3136,6 +3351,14 @@
       <c r="R31" t="n">
         <v>2034</v>
       </c>
+      <c r="FK31" t="n">
+        <v>5</v>
+      </c>
+      <c r="FL31" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="B32" t="n">
@@ -3196,6 +3419,14 @@
       <c r="R32" t="n">
         <v>2031</v>
       </c>
+      <c r="FK32" t="n">
+        <v>5</v>
+      </c>
+      <c r="FL32" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="B33" t="n">
@@ -3261,6 +3492,14 @@
           <t>.</t>
         </is>
       </c>
+      <c r="FK33" t="n">
+        <v>5</v>
+      </c>
+      <c r="FL33" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="B34" t="n">
@@ -3323,6 +3562,14 @@
       <c r="R34" t="n">
         <v>2031</v>
       </c>
+      <c r="FK34" t="n">
+        <v>5</v>
+      </c>
+      <c r="FL34" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="B35" t="n">
@@ -3386,6 +3633,14 @@
       <c r="R35" t="n">
         <v>2033</v>
       </c>
+      <c r="FK35" t="n">
+        <v>5</v>
+      </c>
+      <c r="FL35" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="B36" t="n">
@@ -3446,6 +3701,14 @@
       <c r="R36" t="n">
         <v>2026</v>
       </c>
+      <c r="FK36" t="n">
+        <v>7</v>
+      </c>
+      <c r="FL36" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="B37" t="n">
@@ -3506,6 +3769,14 @@
       <c r="R37" t="n">
         <v>2029</v>
       </c>
+      <c r="FK37" t="n">
+        <v>7</v>
+      </c>
+      <c r="FL37" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="B38" t="n">
@@ -3566,6 +3837,14 @@
       <c r="R38" t="n">
         <v>2030</v>
       </c>
+      <c r="FK38" t="n">
+        <v>7</v>
+      </c>
+      <c r="FL38" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="B39" t="n">
@@ -3626,6 +3905,14 @@
       <c r="R39" t="n">
         <v>2030</v>
       </c>
+      <c r="FK39" t="n">
+        <v>7</v>
+      </c>
+      <c r="FL39" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="B40" t="n">
@@ -3686,6 +3973,14 @@
       <c r="R40" t="n">
         <v>2031</v>
       </c>
+      <c r="FK40" t="n">
+        <v>7</v>
+      </c>
+      <c r="FL40" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="B41" t="n">
@@ -3746,6 +4041,11 @@
       <c r="R41" t="n">
         <v>2037</v>
       </c>
+      <c r="FL41" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="B42" t="n">
@@ -3811,6 +4111,11 @@
       <c r="R42" t="n">
         <v>2038</v>
       </c>
+      <c r="FL42" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="B43" t="n">
@@ -3873,6 +4178,14 @@
       <c r="R43" t="n">
         <v>2034</v>
       </c>
+      <c r="FK43" t="n">
+        <v>7</v>
+      </c>
+      <c r="FL43" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="B44" t="n">
@@ -3933,6 +4246,11 @@
       <c r="R44" t="n">
         <v>2027</v>
       </c>
+      <c r="FL44" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="B45" t="n">
@@ -3993,6 +4311,11 @@
       <c r="R45" t="n">
         <v>2030</v>
       </c>
+      <c r="FL45" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="B46" t="n">
@@ -4053,6 +4376,11 @@
       <c r="R46" t="n">
         <v>2037</v>
       </c>
+      <c r="FL46" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="B47" t="n">
@@ -4111,6 +4439,14 @@
       <c r="R47" t="n">
         <v>2033</v>
       </c>
+      <c r="FK47" t="n">
+        <v>5</v>
+      </c>
+      <c r="FL47" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="B48" t="n">
@@ -4174,6 +4510,14 @@
       <c r="R48" t="n">
         <v>2027</v>
       </c>
+      <c r="FK48" t="n">
+        <v>7</v>
+      </c>
+      <c r="FL48" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="B49" t="n">
@@ -4234,6 +4578,11 @@
       <c r="R49" t="n">
         <v>2033</v>
       </c>
+      <c r="FL49" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="B50" t="n">
@@ -4289,6 +4638,11 @@
       <c r="R50" t="n">
         <v>2033</v>
       </c>
+      <c r="FL50" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="B51" t="n">
@@ -4349,6 +4703,14 @@
       <c r="R51" t="n">
         <v>2031</v>
       </c>
+      <c r="FK51" t="n">
+        <v>5</v>
+      </c>
+      <c r="FL51" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="B52" t="n">
@@ -4411,6 +4773,14 @@
       <c r="R52" t="n">
         <v>2036</v>
       </c>
+      <c r="FK52" t="n">
+        <v>5</v>
+      </c>
+      <c r="FL52" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="B53" t="n">
@@ -4471,6 +4841,14 @@
       <c r="R53" t="n">
         <v>2037</v>
       </c>
+      <c r="FK53" t="n">
+        <v>5</v>
+      </c>
+      <c r="FL53" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="B54" t="n">
@@ -4536,6 +4914,14 @@
       <c r="R54" t="n">
         <v>2028</v>
       </c>
+      <c r="FK54" t="n">
+        <v>7</v>
+      </c>
+      <c r="FL54" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="B55" t="n">
@@ -4596,6 +4982,14 @@
       <c r="R55" t="n">
         <v>2032</v>
       </c>
+      <c r="FK55" t="n">
+        <v>7</v>
+      </c>
+      <c r="FL55" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="B56" t="n">
@@ -4666,6 +5060,14 @@
           <t>.</t>
         </is>
       </c>
+      <c r="FK56" t="n">
+        <v>7</v>
+      </c>
+      <c r="FL56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="B57" t="n">
@@ -4734,6 +5136,14 @@
           <t>.</t>
         </is>
       </c>
+      <c r="FK57" t="n">
+        <v>7</v>
+      </c>
+      <c r="FL57" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="B58" t="n">
@@ -4799,6 +5209,14 @@
           <t>.</t>
         </is>
       </c>
+      <c r="FK58" t="n">
+        <v>7</v>
+      </c>
+      <c r="FL58" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="B59" t="n">
@@ -4862,6 +5280,14 @@
       <c r="R59" t="n">
         <v>2030</v>
       </c>
+      <c r="FK59" t="n">
+        <v>7</v>
+      </c>
+      <c r="FL59" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="B60" t="n">
@@ -4925,6 +5351,14 @@
       <c r="R60" t="n">
         <v>2037</v>
       </c>
+      <c r="FK60" t="n">
+        <v>5</v>
+      </c>
+      <c r="FL60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="B61" t="n">
@@ -4982,6 +5416,11 @@
       <c r="R61" t="n">
         <v>2034</v>
       </c>
+      <c r="FL61" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="B62" t="n">
@@ -5040,6 +5479,11 @@
       <c r="R62" t="n">
         <v>2034</v>
       </c>
+      <c r="FL62" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="B63" t="n">
@@ -5105,6 +5549,11 @@
           <t>S</t>
         </is>
       </c>
+      <c r="FL63" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="B64" t="n">
@@ -5157,6 +5606,14 @@
       <c r="R64" t="n">
         <v>2028</v>
       </c>
+      <c r="FK64" t="n">
+        <v>5</v>
+      </c>
+      <c r="FL64" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="B65" t="n">
@@ -5225,6 +5682,11 @@
           <t>S</t>
         </is>
       </c>
+      <c r="FL65" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="B66" t="n">
@@ -5290,6 +5752,11 @@
       <c r="R66" t="n">
         <v>2034</v>
       </c>
+      <c r="FL66" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="B67" t="n">
@@ -5350,6 +5817,14 @@
       <c r="R67" t="n">
         <v>2028</v>
       </c>
+      <c r="FK67" t="n">
+        <v>7</v>
+      </c>
+      <c r="FL67" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="B68" t="n">
@@ -5412,6 +5887,14 @@
           <t>.</t>
         </is>
       </c>
+      <c r="FK68" t="n">
+        <v>7</v>
+      </c>
+      <c r="FL68" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="B69" t="n">
@@ -5472,6 +5955,14 @@
       <c r="R69" t="n">
         <v>2036</v>
       </c>
+      <c r="FK69" t="n">
+        <v>7</v>
+      </c>
+      <c r="FL69" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="B70" t="n">
@@ -5535,6 +6026,14 @@
       <c r="R70" t="n">
         <v>2037</v>
       </c>
+      <c r="FK70" t="n">
+        <v>7</v>
+      </c>
+      <c r="FL70" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="B71" t="n">
@@ -5595,6 +6094,14 @@
       <c r="R71" t="n">
         <v>2032</v>
       </c>
+      <c r="FK71" t="n">
+        <v>5</v>
+      </c>
+      <c r="FL71" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="B72" t="n">
@@ -5655,6 +6162,14 @@
       <c r="R72" t="n">
         <v>2033</v>
       </c>
+      <c r="FK72" t="n">
+        <v>5</v>
+      </c>
+      <c r="FL72" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="B73" t="n">
@@ -5715,6 +6230,14 @@
       <c r="R73" t="n">
         <v>2035</v>
       </c>
+      <c r="FK73" t="n">
+        <v>5</v>
+      </c>
+      <c r="FL73" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="B74" t="n">
@@ -5775,6 +6298,14 @@
       <c r="R74" t="n">
         <v>2036</v>
       </c>
+      <c r="FK74" t="n">
+        <v>5</v>
+      </c>
+      <c r="FL74" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="B75" t="n">
@@ -5835,6 +6366,14 @@
       <c r="R75" t="n">
         <v>2036</v>
       </c>
+      <c r="FK75" t="n">
+        <v>5</v>
+      </c>
+      <c r="FL75" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="B76" t="n">
@@ -5898,6 +6437,14 @@
       <c r="R76" t="n">
         <v>2037</v>
       </c>
+      <c r="FK76" t="n">
+        <v>5</v>
+      </c>
+      <c r="FL76" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="B77" t="n">
@@ -5958,6 +6505,14 @@
       <c r="R77" t="n">
         <v>2026</v>
       </c>
+      <c r="FK77" t="n">
+        <v>7</v>
+      </c>
+      <c r="FL77" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="B78" t="n">
@@ -6016,6 +6571,14 @@
       <c r="R78" t="n">
         <v>2026</v>
       </c>
+      <c r="FK78" t="n">
+        <v>7</v>
+      </c>
+      <c r="FL78" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="B79" t="n">
@@ -6076,6 +6639,14 @@
       <c r="R79" t="n">
         <v>2028</v>
       </c>
+      <c r="FK79" t="n">
+        <v>7</v>
+      </c>
+      <c r="FL79" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="B80" t="n">
@@ -6136,6 +6707,14 @@
       <c r="R80" t="n">
         <v>2029</v>
       </c>
+      <c r="FK80" t="n">
+        <v>7</v>
+      </c>
+      <c r="FL80" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="B81" t="n">
@@ -6196,6 +6775,14 @@
       <c r="R81" t="n">
         <v>2025</v>
       </c>
+      <c r="FK81" t="n">
+        <v>7</v>
+      </c>
+      <c r="FL81" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="B82" t="n">
@@ -6261,6 +6848,14 @@
       <c r="R82" t="n">
         <v>2026</v>
       </c>
+      <c r="FK82" t="n">
+        <v>7</v>
+      </c>
+      <c r="FL82" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="B83" t="n">
@@ -6318,6 +6913,14 @@
       <c r="R83" t="n">
         <v>2027</v>
       </c>
+      <c r="FK83" t="n">
+        <v>7</v>
+      </c>
+      <c r="FL83" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="B84" t="n">
@@ -6378,6 +6981,14 @@
       <c r="R84" t="n">
         <v>2027</v>
       </c>
+      <c r="FK84" t="n">
+        <v>7</v>
+      </c>
+      <c r="FL84" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="B85" t="n">
@@ -6438,6 +7049,14 @@
       <c r="R85" t="n">
         <v>2028</v>
       </c>
+      <c r="FK85" t="n">
+        <v>7</v>
+      </c>
+      <c r="FL85" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="B86" t="n">
@@ -6503,6 +7122,14 @@
           <t>.</t>
         </is>
       </c>
+      <c r="FK86" t="n">
+        <v>7</v>
+      </c>
+      <c r="FL86" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="B87" t="n">
@@ -6568,6 +7195,14 @@
       <c r="R87" t="n">
         <v>2031</v>
       </c>
+      <c r="FK87" t="n">
+        <v>7</v>
+      </c>
+      <c r="FL87" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="B88" t="n">
@@ -6628,6 +7263,14 @@
       <c r="R88" t="n">
         <v>2027</v>
       </c>
+      <c r="FK88" t="n">
+        <v>7</v>
+      </c>
+      <c r="FL88" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="B89" t="n">
@@ -6688,6 +7331,14 @@
       <c r="R89" t="n">
         <v>2027</v>
       </c>
+      <c r="FK89" t="n">
+        <v>7</v>
+      </c>
+      <c r="FL89" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="B90" t="n">
@@ -6753,6 +7404,11 @@
       <c r="R90" t="n">
         <v>2028</v>
       </c>
+      <c r="FL90" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="B91" t="n">
@@ -6813,6 +7469,11 @@
       <c r="R91" t="n">
         <v>2027</v>
       </c>
+      <c r="FL91" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="B92" t="n">
@@ -6876,6 +7537,11 @@
       <c r="R92" t="n">
         <v>2030</v>
       </c>
+      <c r="FL92" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="B93" t="n">
@@ -6941,6 +7607,11 @@
           <t>S</t>
         </is>
       </c>
+      <c r="FL93" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="B94" t="n">
@@ -7003,6 +7674,14 @@
       <c r="R94" t="n">
         <v>2026</v>
       </c>
+      <c r="FK94" t="n">
+        <v>5</v>
+      </c>
+      <c r="FL94" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="B95" t="n">
@@ -7068,6 +7747,14 @@
           <t>S</t>
         </is>
       </c>
+      <c r="FK95" t="n">
+        <v>5</v>
+      </c>
+      <c r="FL95" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="B96" t="n">
@@ -7128,6 +7815,11 @@
       <c r="R96" t="n">
         <v>2028</v>
       </c>
+      <c r="FL96" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="B97" t="n">
@@ -7185,6 +7877,11 @@
       <c r="R97" t="n">
         <v>2030</v>
       </c>
+      <c r="FL97" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="B98" t="n">
@@ -7237,6 +7934,11 @@
       <c r="R98" t="n">
         <v>2028</v>
       </c>
+      <c r="FL98" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="B99" t="n">
@@ -7304,6 +8006,14 @@
           <t>.</t>
         </is>
       </c>
+      <c r="FK99" t="n">
+        <v>5</v>
+      </c>
+      <c r="FL99" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="B100" t="n">
@@ -7364,6 +8074,14 @@
       <c r="R100" t="n">
         <v>2029</v>
       </c>
+      <c r="FK100" t="n">
+        <v>5</v>
+      </c>
+      <c r="FL100" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="B101" t="n">
@@ -7424,6 +8142,11 @@
       <c r="R101" t="n">
         <v>2028</v>
       </c>
+      <c r="FL101" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="B102" t="n">
@@ -7484,6 +8207,11 @@
       <c r="R102" t="n">
         <v>2026</v>
       </c>
+      <c r="FL102" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="B103" t="n">
@@ -7544,6 +8272,11 @@
       <c r="R103" t="n">
         <v>2028</v>
       </c>
+      <c r="FL103" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="B104" t="n">
@@ -7609,6 +8342,11 @@
           <t>S</t>
         </is>
       </c>
+      <c r="FL104" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="B105" t="n">
@@ -7674,6 +8412,11 @@
           <t>S</t>
         </is>
       </c>
+      <c r="FL105" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="B106" t="n">
@@ -7734,6 +8477,11 @@
       <c r="R106" t="n">
         <v>2028</v>
       </c>
+      <c r="FL106" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="B107" t="n">
@@ -7804,6 +8552,11 @@
           <t>S</t>
         </is>
       </c>
+      <c r="FL107" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="B108" t="n">
@@ -7867,6 +8620,14 @@
       <c r="R108" t="n">
         <v>2027</v>
       </c>
+      <c r="FK108" t="n">
+        <v>5</v>
+      </c>
+      <c r="FL108" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="B109" t="n">
@@ -7927,6 +8688,14 @@
       <c r="R109" t="n">
         <v>2028</v>
       </c>
+      <c r="FK109" t="n">
+        <v>5</v>
+      </c>
+      <c r="FL109" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="B110" t="n">
@@ -7987,6 +8756,14 @@
       <c r="R110" t="n">
         <v>2028</v>
       </c>
+      <c r="FK110" t="n">
+        <v>5</v>
+      </c>
+      <c r="FL110" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="B111" t="n">
@@ -8052,6 +8829,11 @@
       <c r="R111" t="n">
         <v>2029</v>
       </c>
+      <c r="FL111" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="B112" t="n">
@@ -8112,6 +8894,14 @@
       <c r="R112" t="n">
         <v>2024</v>
       </c>
+      <c r="FK112" t="n">
+        <v>5</v>
+      </c>
+      <c r="FL112" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="B113" t="n">
@@ -8174,6 +8964,14 @@
       <c r="R113" t="n">
         <v>2026</v>
       </c>
+      <c r="FK113" t="n">
+        <v>5</v>
+      </c>
+      <c r="FL113" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="B114" t="n">
@@ -8234,6 +9032,14 @@
       <c r="R114" t="n">
         <v>2027</v>
       </c>
+      <c r="FK114" t="n">
+        <v>5</v>
+      </c>
+      <c r="FL114" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="B115" t="n">
@@ -8297,6 +9103,14 @@
           <t>S</t>
         </is>
       </c>
+      <c r="FK115" t="n">
+        <v>5</v>
+      </c>
+      <c r="FL115" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="B116" t="n">
@@ -8357,6 +9171,14 @@
       <c r="R116" t="n">
         <v>2030</v>
       </c>
+      <c r="FK116" t="n">
+        <v>5</v>
+      </c>
+      <c r="FL116" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="B117" t="n">
@@ -8420,6 +9242,14 @@
       <c r="R117" t="n">
         <v>2031</v>
       </c>
+      <c r="FK117" t="n">
+        <v>5</v>
+      </c>
+      <c r="FL117" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="B118" t="n">
@@ -8478,6 +9308,14 @@
       <c r="R118" t="n">
         <v>2032</v>
       </c>
+      <c r="FK118" t="n">
+        <v>5</v>
+      </c>
+      <c r="FL118" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="B119" t="n">
@@ -8541,6 +9379,14 @@
       <c r="R119" t="n">
         <v>2037</v>
       </c>
+      <c r="FK119" t="n">
+        <v>5</v>
+      </c>
+      <c r="FL119" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="B120" t="n">
@@ -8601,6 +9447,14 @@
       <c r="R120" t="n">
         <v>2030</v>
       </c>
+      <c r="FK120" t="n">
+        <v>5</v>
+      </c>
+      <c r="FL120" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="B121" t="n">
@@ -8666,6 +9520,14 @@
           <t>S</t>
         </is>
       </c>
+      <c r="FK121" t="n">
+        <v>5</v>
+      </c>
+      <c r="FL121" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="B122" t="n">
@@ -8726,6 +9588,14 @@
       <c r="R122" t="n">
         <v>2038</v>
       </c>
+      <c r="FK122" t="n">
+        <v>5</v>
+      </c>
+      <c r="FL122" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="B123" t="n">
@@ -8791,6 +9661,14 @@
           <t>S</t>
         </is>
       </c>
+      <c r="FK123" t="n">
+        <v>5</v>
+      </c>
+      <c r="FL123" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="B124" t="n">
@@ -8851,6 +9729,14 @@
       <c r="R124" t="n">
         <v>2028</v>
       </c>
+      <c r="FK124" t="n">
+        <v>5</v>
+      </c>
+      <c r="FL124" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="B125" t="n">
@@ -8911,6 +9797,14 @@
       <c r="R125" t="n">
         <v>2034</v>
       </c>
+      <c r="FK125" t="n">
+        <v>5</v>
+      </c>
+      <c r="FL125" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="B126" t="n">
@@ -8973,6 +9867,14 @@
       <c r="R126" t="n">
         <v>2032</v>
       </c>
+      <c r="FK126" t="n">
+        <v>5</v>
+      </c>
+      <c r="FL126" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="B127" t="n">
@@ -9033,6 +9935,14 @@
       <c r="R127" t="n">
         <v>2033</v>
       </c>
+      <c r="FK127" t="n">
+        <v>5</v>
+      </c>
+      <c r="FL127" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="B128" t="n">
@@ -9101,6 +10011,11 @@
       <c r="R128" t="n">
         <v>2037</v>
       </c>
+      <c r="FL128" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="B129" t="n">
@@ -9161,6 +10076,14 @@
       <c r="R129" t="n">
         <v>2031</v>
       </c>
+      <c r="FK129" t="n">
+        <v>5</v>
+      </c>
+      <c r="FL129" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="B130" t="n">
@@ -9221,6 +10144,14 @@
       <c r="R130" t="n">
         <v>2025</v>
       </c>
+      <c r="FK130" t="n">
+        <v>5</v>
+      </c>
+      <c r="FL130" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="B131" t="n">
@@ -9281,6 +10212,14 @@
       <c r="R131" t="n">
         <v>2026</v>
       </c>
+      <c r="FK131" t="n">
+        <v>5</v>
+      </c>
+      <c r="FL131" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="B132" t="n">
@@ -9344,6 +10283,14 @@
       <c r="R132" t="n">
         <v>2027</v>
       </c>
+      <c r="FK132" t="n">
+        <v>5</v>
+      </c>
+      <c r="FL132" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="B133" t="n">
@@ -9409,6 +10356,14 @@
       <c r="R133" t="n">
         <v>2027</v>
       </c>
+      <c r="FK133" t="n">
+        <v>5</v>
+      </c>
+      <c r="FL133" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="B134" t="n">
@@ -9469,6 +10424,14 @@
       <c r="R134" t="n">
         <v>2035</v>
       </c>
+      <c r="FK134" t="n">
+        <v>5</v>
+      </c>
+      <c r="FL134" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="B135" t="n">
@@ -9521,6 +10484,14 @@
       <c r="R135" t="n">
         <v>2031</v>
       </c>
+      <c r="FK135" t="n">
+        <v>5</v>
+      </c>
+      <c r="FL135" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="B136" t="n">
@@ -9581,6 +10552,14 @@
       <c r="R136" t="n">
         <v>2026</v>
       </c>
+      <c r="FK136" t="n">
+        <v>5</v>
+      </c>
+      <c r="FL136" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="B137" t="n">
@@ -9641,6 +10620,14 @@
       <c r="R137" t="n">
         <v>2029</v>
       </c>
+      <c r="FK137" t="n">
+        <v>5</v>
+      </c>
+      <c r="FL137" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="B138" t="n">
@@ -9696,6 +10683,14 @@
       <c r="R138" t="n">
         <v>2027</v>
       </c>
+      <c r="FK138" t="n">
+        <v>5</v>
+      </c>
+      <c r="FL138" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="B139" t="n">
@@ -9751,6 +10746,14 @@
       <c r="R139" t="n">
         <v>2027</v>
       </c>
+      <c r="FK139" t="n">
+        <v>5</v>
+      </c>
+      <c r="FL139" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="B140" t="n">
@@ -9811,6 +10814,14 @@
       <c r="R140" t="n">
         <v>2028</v>
       </c>
+      <c r="FK140" t="n">
+        <v>5</v>
+      </c>
+      <c r="FL140" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="B141" t="n">
@@ -9876,6 +10887,14 @@
           <t>.</t>
         </is>
       </c>
+      <c r="FK141" t="n">
+        <v>5</v>
+      </c>
+      <c r="FL141" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="B142" t="n">
@@ -9936,6 +10955,14 @@
       <c r="R142" t="n">
         <v>2031</v>
       </c>
+      <c r="FK142" t="n">
+        <v>5</v>
+      </c>
+      <c r="FL142" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="B143" t="n">
@@ -9996,6 +11023,14 @@
       <c r="R143" t="n">
         <v>2031</v>
       </c>
+      <c r="FK143" t="n">
+        <v>5</v>
+      </c>
+      <c r="FL143" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="B144" t="n">
@@ -10061,6 +11096,14 @@
           <t>S</t>
         </is>
       </c>
+      <c r="FK144" t="n">
+        <v>5</v>
+      </c>
+      <c r="FL144" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="B145" t="n">
@@ -10126,6 +11169,14 @@
           <t>S</t>
         </is>
       </c>
+      <c r="FK145" t="n">
+        <v>5</v>
+      </c>
+      <c r="FL145" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="B146" t="n">
@@ -10186,6 +11237,14 @@
       <c r="R146" t="n">
         <v>2030</v>
       </c>
+      <c r="FK146" t="n">
+        <v>5</v>
+      </c>
+      <c r="FL146" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="B147" t="n">
@@ -10249,6 +11308,14 @@
       <c r="R147" t="n">
         <v>2026</v>
       </c>
+      <c r="FK147" t="n">
+        <v>5</v>
+      </c>
+      <c r="FL147" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="B148" t="n">
@@ -10309,6 +11376,14 @@
       <c r="R148" t="n">
         <v>2027</v>
       </c>
+      <c r="FK148" t="n">
+        <v>5</v>
+      </c>
+      <c r="FL148" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="B149" t="n">
@@ -10369,6 +11444,14 @@
       <c r="R149" t="n">
         <v>2027</v>
       </c>
+      <c r="FK149" t="n">
+        <v>5</v>
+      </c>
+      <c r="FL149" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="B150" t="n">
@@ -10429,6 +11512,14 @@
       <c r="R150" t="n">
         <v>2030</v>
       </c>
+      <c r="FK150" t="n">
+        <v>5</v>
+      </c>
+      <c r="FL150" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="B151" t="n">
@@ -10489,6 +11580,14 @@
       <c r="R151" t="n">
         <v>2031</v>
       </c>
+      <c r="FK151" t="n">
+        <v>5</v>
+      </c>
+      <c r="FL151" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="B152" t="n">
@@ -10551,6 +11650,14 @@
       <c r="R152" t="n">
         <v>2032</v>
       </c>
+      <c r="FK152" t="n">
+        <v>5</v>
+      </c>
+      <c r="FL152" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="B153" t="n">
@@ -10606,6 +11713,14 @@
       <c r="R153" t="n">
         <v>2026</v>
       </c>
+      <c r="FK153" t="n">
+        <v>5</v>
+      </c>
+      <c r="FL153" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="B154" t="n">
@@ -10666,6 +11781,14 @@
       <c r="R154" t="n">
         <v>2026</v>
       </c>
+      <c r="FK154" t="n">
+        <v>5</v>
+      </c>
+      <c r="FL154" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="B155" t="n">
@@ -10726,6 +11849,14 @@
       <c r="R155" t="n">
         <v>2026</v>
       </c>
+      <c r="FK155" t="n">
+        <v>5</v>
+      </c>
+      <c r="FL155" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="B156" t="n">
@@ -10786,6 +11917,14 @@
       <c r="R156" t="n">
         <v>2027</v>
       </c>
+      <c r="FK156" t="n">
+        <v>5</v>
+      </c>
+      <c r="FL156" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="B157" t="n">
@@ -10846,6 +11985,14 @@
       <c r="R157" t="n">
         <v>2027</v>
       </c>
+      <c r="FK157" t="n">
+        <v>5</v>
+      </c>
+      <c r="FL157" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="B158" t="n">
@@ -10908,6 +12055,14 @@
       <c r="R158" t="n">
         <v>2027</v>
       </c>
+      <c r="FK158" t="n">
+        <v>5</v>
+      </c>
+      <c r="FL158" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="B159" t="n">
@@ -10968,6 +12123,11 @@
       <c r="R159" t="n">
         <v>2038</v>
       </c>
+      <c r="FL159" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="B160" t="n">
@@ -11033,6 +12193,14 @@
           <t>.</t>
         </is>
       </c>
+      <c r="FK160" t="n">
+        <v>5</v>
+      </c>
+      <c r="FL160" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="B161" t="n">
@@ -11088,6 +12256,14 @@
       <c r="R161" t="n">
         <v>2031</v>
       </c>
+      <c r="FK161" t="n">
+        <v>5</v>
+      </c>
+      <c r="FL161" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="B162" t="n">
@@ -11153,6 +12329,14 @@
           <t>.</t>
         </is>
       </c>
+      <c r="FK162" t="n">
+        <v>5</v>
+      </c>
+      <c r="FL162" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="B163" t="n">
@@ -11213,6 +12397,14 @@
       <c r="R163" t="n">
         <v>2026</v>
       </c>
+      <c r="FK163" t="n">
+        <v>5</v>
+      </c>
+      <c r="FL163" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="B164" t="n">
@@ -11273,6 +12465,14 @@
       <c r="R164" t="n">
         <v>2026</v>
       </c>
+      <c r="FK164" t="n">
+        <v>5</v>
+      </c>
+      <c r="FL164" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="B165" t="n">
@@ -11328,6 +12528,14 @@
       <c r="R165" t="n">
         <v>2028</v>
       </c>
+      <c r="FK165" t="n">
+        <v>5</v>
+      </c>
+      <c r="FL165" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="B166" t="n">
@@ -11391,6 +12599,14 @@
       <c r="R166" t="n">
         <v>2029</v>
       </c>
+      <c r="FK166" t="n">
+        <v>5</v>
+      </c>
+      <c r="FL166" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="B167" t="n">
@@ -11448,6 +12664,14 @@
       <c r="R167" t="n">
         <v>2030</v>
       </c>
+      <c r="FK167" t="n">
+        <v>5</v>
+      </c>
+      <c r="FL167" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="B168" t="n">
@@ -11510,6 +12734,14 @@
       <c r="R168" t="n">
         <v>2028</v>
       </c>
+      <c r="FK168" t="n">
+        <v>5</v>
+      </c>
+      <c r="FL168" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="B169" t="n">
@@ -11565,6 +12797,14 @@
       <c r="R169" t="n">
         <v>2027</v>
       </c>
+      <c r="FK169" t="n">
+        <v>5</v>
+      </c>
+      <c r="FL169" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="B170" t="n">
@@ -11630,6 +12870,14 @@
       <c r="R170" t="n">
         <v>2030</v>
       </c>
+      <c r="FK170" t="n">
+        <v>5</v>
+      </c>
+      <c r="FL170" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="B171" t="n">
@@ -11690,6 +12938,14 @@
       <c r="R171" t="n">
         <v>2031</v>
       </c>
+      <c r="FK171" t="n">
+        <v>5</v>
+      </c>
+      <c r="FL171" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="B172" t="n">
@@ -11757,6 +13013,14 @@
           <t>.</t>
         </is>
       </c>
+      <c r="FK172" t="n">
+        <v>5</v>
+      </c>
+      <c r="FL172" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="B173" t="n">
@@ -11817,6 +13081,14 @@
       <c r="R173" t="n">
         <v>2024</v>
       </c>
+      <c r="FK173" t="n">
+        <v>5</v>
+      </c>
+      <c r="FL173" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="B174" t="n">
@@ -11877,6 +13149,14 @@
       <c r="R174" t="n">
         <v>2026</v>
       </c>
+      <c r="FK174" t="n">
+        <v>5</v>
+      </c>
+      <c r="FL174" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="B175" t="n">
@@ -11935,6 +13215,14 @@
       <c r="R175" t="n">
         <v>2027</v>
       </c>
+      <c r="FK175" t="n">
+        <v>5</v>
+      </c>
+      <c r="FL175" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="B176" t="n">
@@ -11995,6 +13283,14 @@
       <c r="R176" t="n">
         <v>2027</v>
       </c>
+      <c r="FK176" t="n">
+        <v>5</v>
+      </c>
+      <c r="FL176" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="B177" t="n">
@@ -12058,6 +13354,14 @@
       <c r="R177" t="n">
         <v>2032</v>
       </c>
+      <c r="FK177" t="n">
+        <v>5</v>
+      </c>
+      <c r="FL177" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="B178" t="n">
@@ -12118,6 +13422,14 @@
       <c r="R178" t="n">
         <v>2030</v>
       </c>
+      <c r="FK178" t="n">
+        <v>5</v>
+      </c>
+      <c r="FL178" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="B179" t="n">
@@ -12170,6 +13482,14 @@
       <c r="R179" t="n">
         <v>2025</v>
       </c>
+      <c r="FK179" t="n">
+        <v>5</v>
+      </c>
+      <c r="FL179" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="B180" t="n">
@@ -12222,6 +13542,14 @@
       <c r="R180" t="n">
         <v>2026</v>
       </c>
+      <c r="FK180" t="n">
+        <v>5</v>
+      </c>
+      <c r="FL180" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="B181" t="n">
@@ -12282,6 +13610,14 @@
       <c r="R181" t="n">
         <v>2026</v>
       </c>
+      <c r="FK181" t="n">
+        <v>5</v>
+      </c>
+      <c r="FL181" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="B182" t="n">
@@ -12347,6 +13683,14 @@
       <c r="R182" t="n">
         <v>2027</v>
       </c>
+      <c r="FK182" t="n">
+        <v>5</v>
+      </c>
+      <c r="FL182" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="B183" t="n">
@@ -12407,6 +13751,14 @@
       <c r="R183" t="n">
         <v>2029</v>
       </c>
+      <c r="FK183" t="n">
+        <v>5</v>
+      </c>
+      <c r="FL183" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="B184" t="n">
@@ -12467,6 +13819,14 @@
       <c r="R184" t="n">
         <v>2033</v>
       </c>
+      <c r="FK184" t="n">
+        <v>5</v>
+      </c>
+      <c r="FL184" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="B185" t="n">
@@ -12527,6 +13887,14 @@
       <c r="R185" t="n">
         <v>2026</v>
       </c>
+      <c r="FK185" t="n">
+        <v>5</v>
+      </c>
+      <c r="FL185" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="B186" t="n">
@@ -12590,6 +13958,11 @@
       <c r="R186" t="n">
         <v>2029</v>
       </c>
+      <c r="FL186" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="B187" t="n">
@@ -12650,6 +14023,14 @@
       <c r="R187" t="n">
         <v>2026</v>
       </c>
+      <c r="FK187" t="n">
+        <v>5</v>
+      </c>
+      <c r="FL187" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="B188" t="n">
@@ -12710,6 +14091,14 @@
       <c r="R188" t="n">
         <v>2026</v>
       </c>
+      <c r="FK188" t="n">
+        <v>5</v>
+      </c>
+      <c r="FL188" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="B189" t="n">
@@ -12775,6 +14164,14 @@
       <c r="R189" t="n">
         <v>2029</v>
       </c>
+      <c r="FK189" t="n">
+        <v>7</v>
+      </c>
+      <c r="FL189" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="B190" t="n">
@@ -12835,6 +14232,14 @@
       <c r="R190" t="n">
         <v>2033</v>
       </c>
+      <c r="FK190" t="n">
+        <v>5</v>
+      </c>
+      <c r="FL190" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="B191" t="n">
@@ -12902,6 +14307,14 @@
           <t>.</t>
         </is>
       </c>
+      <c r="FK191" t="n">
+        <v>5</v>
+      </c>
+      <c r="FL191" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="B192" t="n">
@@ -12962,6 +14375,14 @@
       <c r="R192" t="n">
         <v>2031</v>
       </c>
+      <c r="FK192" t="n">
+        <v>5</v>
+      </c>
+      <c r="FL192" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="B193" t="n">
@@ -13022,6 +14443,14 @@
       <c r="R193" t="n">
         <v>2025</v>
       </c>
+      <c r="FK193" t="n">
+        <v>5</v>
+      </c>
+      <c r="FL193" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="B194" t="n">
@@ -13082,6 +14511,14 @@
       <c r="R194" t="n">
         <v>2031</v>
       </c>
+      <c r="FK194" t="n">
+        <v>5</v>
+      </c>
+      <c r="FL194" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="B195" t="n">
@@ -13142,6 +14579,11 @@
       <c r="R195" t="n">
         <v>2029</v>
       </c>
+      <c r="FL195" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="B196" t="n">
@@ -13202,6 +14644,11 @@
       <c r="R196" t="n">
         <v>2026</v>
       </c>
+      <c r="FL196" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="B197" t="n">
@@ -13262,6 +14709,14 @@
       <c r="R197" t="n">
         <v>2031</v>
       </c>
+      <c r="FK197" t="n">
+        <v>5</v>
+      </c>
+      <c r="FL197" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="B198" t="n">
@@ -13330,6 +14785,14 @@
           <t>.</t>
         </is>
       </c>
+      <c r="FK198" t="n">
+        <v>5</v>
+      </c>
+      <c r="FL198" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="B199" t="n">
@@ -13390,6 +14853,14 @@
       <c r="R199" t="n">
         <v>2029</v>
       </c>
+      <c r="FK199" t="n">
+        <v>5</v>
+      </c>
+      <c r="FL199" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="B200" t="n">
@@ -13463,6 +14934,14 @@
           <t>.</t>
         </is>
       </c>
+      <c r="FK200" t="n">
+        <v>5</v>
+      </c>
+      <c r="FL200" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="B201" t="n">
@@ -13529,6 +15008,14 @@
       <c r="S201" t="inlineStr">
         <is>
           <t>.</t>
+        </is>
+      </c>
+      <c r="FK201" t="n">
+        <v>5</v>
+      </c>
+      <c r="FL201" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
     </row>
